--- a/PDF/1.1. SOLICITA CRIAÇÃO DE FUNÇÃO.xlsx
+++ b/PDF/1.1. SOLICITA CRIAÇÃO DE FUNÇÃO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr codeName="EstaPasta_de_trabalho" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\___TEXTOS PRONTOS - FLÁVIA\7. ADENDO DE FUNÇÃO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8FF87B-5329-4C29-A5A2-4BAA657A310F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E129A92F-6D8F-4E2B-AE50-BC41470E0E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
   <si>
     <t>SOLICITAÇÃO DE ADENDO DE FUNÇÃO</t>
   </si>
@@ -127,9 +127,6 @@
     <t>4. SETOR DA NOVA FUNÇÃO:</t>
   </si>
   <si>
-    <t>5. FUNÇÃO SEMELHANTE:</t>
-  </si>
-  <si>
     <t>6. NÚMERO DE FUNCIONÁRIO NESTA NOVA FUNÇÃO:</t>
   </si>
   <si>
@@ -137,44 +134,6 @@
   </si>
   <si>
     <t>8. NOME DO SOLICITANTE:</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Enviar a solicitação para os emails:  MAYLON - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>seguranca01@mednet-osasco.com.br</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> / DONIZETE TRINCA - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">gestorprocessos@mednet-osasco.com.br </t>
-    </r>
   </si>
   <si>
     <r>
@@ -220,9 +179,6 @@
     <t>CONTATO COM MICROORGANISMOS (VÍRUS, BACTÉRIAS, FUNGOS, ETC.)</t>
   </si>
   <si>
-    <t>1. EMPRESA + CNPJ</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">PRAZO PARA O MÉDICO ASSINAR NOVO PCMSO E LIBERAR PARA EXAMES É DE ATÉ </t>
     </r>
@@ -239,12 +195,84 @@
       <t>48 HORAS ÚTEIS.</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Enviar a solicitação para os emails:  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>seguranca@mednet-osasco.com.br</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / DONIZETE TRINCA - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">gestorprocessos@mednet-osasco.com.br </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FUNÇÃO SEMELHANTE:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(PRESENTE EM SEUS DOCUMENTOS)</t>
+    </r>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>1. EMPRESA / UNIDADE / CNPJ:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,8 +350,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,8 +384,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B480"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -607,11 +649,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
@@ -622,26 +677,41 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -651,20 +721,32 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -674,11 +756,63 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -725,113 +859,40 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -839,6 +900,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF4B480"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -848,73 +914,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
-<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{8BD21D10-EC42-11CE-9E0D-00AA006002F3}" ax:persistence="persistStreamInit" r:id="rId1"/>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>10</xdr:col>
-          <xdr:colOff>104775</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="1028" name="TextBox1" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1028"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:noFill/>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1203,11 +1202,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Plan1"/>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="3" width="11.7109375" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="11.7109375" customWidth="1"/>
@@ -1217,285 +1217,284 @@
     <col min="13" max="13" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:12" ht="24" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="50"/>
-    </row>
-    <row r="2" spans="1:11" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="42"/>
-    </row>
-    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="13"/>
+    </row>
+    <row r="2" spans="1:12" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="10"/>
+    </row>
+    <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="26"/>
+    </row>
+    <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="29"/>
+    </row>
+    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+    </row>
+    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="29"/>
+    </row>
+    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="39" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="60"/>
-    </row>
-    <row r="4" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="20"/>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="20"/>
-    </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="20"/>
-    </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="29"/>
+    </row>
+    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20"/>
-    </row>
-    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="46" t="s">
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="69"/>
+    </row>
+    <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="13"/>
-    </row>
-    <row r="9" spans="1:11" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="46" t="s">
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="66"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="65" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="66"/>
+      <c r="I9" s="66"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="67"/>
+    </row>
+    <row r="10" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+      <c r="K10" s="29"/>
+    </row>
+    <row r="11" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20"/>
-    </row>
-    <row r="10" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="54"/>
-      <c r="I10" s="54"/>
-      <c r="J10" s="54"/>
-      <c r="K10" s="55"/>
-    </row>
-    <row r="11" spans="1:11" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="65"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="68"/>
-    </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="43" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="19"/>
+    </row>
+    <row r="12" spans="1:12" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="33"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="36"/>
+    </row>
+    <row r="13" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="45"/>
-    </row>
-    <row r="13" spans="1:11" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="7"/>
-    </row>
-    <row r="14" spans="1:11" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="62"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="63"/>
-      <c r="K14" s="64"/>
-    </row>
-    <row r="15" spans="1:11" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="58"/>
-    </row>
-    <row r="16" spans="1:11" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="40"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="42"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="38" t="s">
+      <c r="B13" s="71"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="72"/>
+    </row>
+    <row r="14" spans="1:12" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="61"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="63"/>
+    </row>
+    <row r="15" spans="1:12" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="30"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="32"/>
+    </row>
+    <row r="16" spans="1:12" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="24"/>
+    </row>
+    <row r="17" spans="1:11" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="1" t="s">
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="2"/>
-      <c r="K17" s="3" t="s">
+      <c r="J18" s="2"/>
+      <c r="K18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
       <c r="I19" t="s">
         <v>13</v>
       </c>
@@ -1505,16 +1504,16 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
+      <c r="A20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
       <c r="I20" t="s">
         <v>13</v>
       </c>
@@ -1524,16 +1523,16 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
+      <c r="A21" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
       <c r="I21" t="s">
         <v>13</v>
       </c>
@@ -1543,16 +1542,16 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
+      <c r="A22" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
       <c r="I22" t="s">
         <v>13</v>
       </c>
@@ -1562,16 +1561,16 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
+      <c r="A23" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
       <c r="I23" t="s">
         <v>13</v>
       </c>
@@ -1581,16 +1580,16 @@
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
+      <c r="A24" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
       <c r="I24" t="s">
         <v>13</v>
       </c>
@@ -1600,16 +1599,16 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="A25" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
       <c r="I25" t="s">
         <v>13</v>
       </c>
@@ -1619,16 +1618,16 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
+      <c r="A26" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
       <c r="I26" t="s">
         <v>13</v>
       </c>
@@ -1638,16 +1637,16 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="A27" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
       <c r="I27" t="s">
         <v>13</v>
       </c>
@@ -1657,16 +1656,16 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
+      <c r="A28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
       <c r="I28" t="s">
         <v>13</v>
       </c>
@@ -1676,16 +1675,16 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
+      <c r="A29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
       <c r="I29" t="s">
         <v>13</v>
       </c>
@@ -1695,16 +1694,16 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
+      <c r="A30" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
       <c r="I30" t="s">
         <v>13</v>
       </c>
@@ -1714,16 +1713,16 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="22"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
+      <c r="A31" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
       <c r="I31" t="s">
         <v>13</v>
       </c>
@@ -1733,16 +1732,16 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
+      <c r="A32" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
       <c r="I32" t="s">
         <v>13</v>
       </c>
@@ -1752,16 +1751,16 @@
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
+      <c r="A33" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
       <c r="I33" t="s">
         <v>13</v>
       </c>
@@ -1771,16 +1770,16 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
+      <c r="A34" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
       <c r="I34" t="s">
         <v>13</v>
       </c>
@@ -1790,16 +1789,16 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
+      <c r="A35" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
       <c r="I35" t="s">
         <v>13</v>
       </c>
@@ -1809,16 +1808,16 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
+      <c r="A36" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
       <c r="I36" t="s">
         <v>13</v>
       </c>
@@ -1827,17 +1826,17 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
       <c r="I37" t="s">
         <v>13</v>
       </c>
@@ -1846,254 +1845,248 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="16"/>
+    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" t="s">
+        <v>13</v>
+      </c>
+      <c r="J38" s="4"/>
+      <c r="K38" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="39" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="16"/>
+      <c r="A39" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="47"/>
     </row>
     <row r="40" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="51" t="s">
+      <c r="A40" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="46"/>
+      <c r="C40" s="46"/>
+      <c r="D40" s="46"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="46"/>
+      <c r="H40" s="46"/>
+      <c r="I40" s="46"/>
+      <c r="J40" s="46"/>
+      <c r="K40" s="47"/>
+    </row>
+    <row r="41" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="52"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="53"/>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="32" t="s">
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="16"/>
+    </row>
+    <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="34"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="23"/>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24"/>
-      <c r="E42" s="24"/>
-      <c r="F42" s="24"/>
-      <c r="G42" s="24"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="25"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="59"/>
+      <c r="K42" s="60"/>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="26"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="28"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="50"/>
+      <c r="J43" s="50"/>
+      <c r="K43" s="51"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="26"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="28"/>
+      <c r="A44" s="52"/>
+      <c r="B44" s="53"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="53"/>
+      <c r="H44" s="53"/>
+      <c r="I44" s="53"/>
+      <c r="J44" s="53"/>
+      <c r="K44" s="54"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="26"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="28"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="54"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="26"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="28"/>
+      <c r="A46" s="52"/>
+      <c r="B46" s="53"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="54"/>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="26"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="28"/>
-    </row>
-    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="29"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="31"/>
-    </row>
-    <row r="49" spans="1:11" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="16"/>
+      <c r="A47" s="52"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="53"/>
+      <c r="K47" s="54"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="52"/>
+      <c r="B48" s="53"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="54"/>
+    </row>
+    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="55"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="57"/>
+    </row>
+    <row r="50" spans="1:11" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="48" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" s="46"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="46"/>
+      <c r="G50" s="46"/>
+      <c r="H50" s="46"/>
+      <c r="I50" s="46"/>
+      <c r="J50" s="46"/>
+      <c r="K50" s="47"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="46">
+  <mergeCells count="50">
+    <mergeCell ref="D8:K8"/>
+    <mergeCell ref="A9:C10"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A43:K49"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A14:K14"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A16:K16"/>
     <mergeCell ref="D3:K3"/>
     <mergeCell ref="D4:K4"/>
     <mergeCell ref="D5:K5"/>
     <mergeCell ref="D7:K7"/>
-    <mergeCell ref="A14:K14"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A34:H34"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A12:K12"/>
     <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="A49:K49"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A42:K48"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="A18:H18"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="1028" r:id="rId4" name="TextBox1">
-          <controlPr defaultSize="0" autoLine="0" r:id="rId5">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>0</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>12</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>10</xdr:col>
-                <xdr:colOff>104775</xdr:colOff>
-                <xdr:row>13</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="1028" r:id="rId4" name="TextBox1"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
 </worksheet>
 </file>
 
